--- a/data/trans_orig/IMC_inf_MED_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5450</t>
+          <t>5495</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>13463</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11784</t>
+          <t>11661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>11866</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22409</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>585</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>579</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5088</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>7423</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3837</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11135</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2078</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8665</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7818</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17470</t>
+          <t>17521</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6592</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14775</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6372</t>
+          <t>6586</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15564</t>
+          <t>14776</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26852</t>
+          <t>25991</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>650</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6295</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>633</t>
+          <t>642</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1949</t>
+          <t>1930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8936</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,6%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27006</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44237</t>
+          <t>44702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>48509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70951</t>
+          <t>69573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81371</t>
+          <t>81733</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109480</t>
+          <t>110478</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18277</t>
+          <t>18473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33578</t>
+          <t>34070</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>25162</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42306</t>
+          <t>41825</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47524</t>
+          <t>47758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>70817</t>
+          <t>71164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26948</t>
+          <t>26983</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44807</t>
+          <t>44237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>30448</t>
+          <t>30109</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49133</t>
+          <t>48848</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62980</t>
+          <t>62929</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89394</t>
+          <t>88887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72889</t>
+          <t>73817</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95740</t>
+          <t>97043</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>56798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>80204</t>
+          <t>79492</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>135966</t>
+          <t>135669</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169225</t>
+          <t>167306</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>42,14%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13459</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15794</t>
+          <t>16274</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>11410</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26295</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5122</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14575</t>
+          <t>14416</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22559</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17564</t>
+          <t>17846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33153</t>
+          <t>32872</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14259</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27189</t>
+          <t>27982</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>12701</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>25906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29242</t>
+          <t>29464</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48454</t>
+          <t>47925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>33218</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>50929</t>
+          <t>50796</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30342</t>
+          <t>30486</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>47791</t>
+          <t>48369</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68089</t>
+          <t>68834</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92918</t>
+          <t>92768</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>34,89%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48866</t>
+          <t>47856</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67451</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49250</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>68131</t>
+          <t>68473</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>51,13%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>104029</t>
+          <t>103499</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130135</t>
+          <t>129580</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,74%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>837</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7627</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>11691</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>5115</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6808</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>12533</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16523</t>
+          <t>16830</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12255</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>25634</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>41761</t>
+          <t>40631</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42729</t>
+          <t>42555</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>61768</t>
+          <t>61333</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>40,02%</t>
+          <t>39,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71177</t>
+          <t>71565</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>96304</t>
+          <t>97515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>32,1%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>94128</t>
+          <t>95930</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>113893</t>
+          <t>114642</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>77625</t>
+          <t>77884</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>96691</t>
+          <t>97002</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>178592</t>
+          <t>179027</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>205692</t>
+          <t>206972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,14%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1855</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>682</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3301</t>
+          <t>3364</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11149</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69511</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>99292</t>
+          <t>99828</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>121079</t>
+          <t>120901</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>158173</t>
+          <t>156064</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>67086</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51670</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76430</t>
+          <t>77857</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>102188</t>
+          <t>101551</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>135198</t>
+          <t>135457</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100942</t>
+          <t>101983</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>132384</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118765</t>
+          <t>119627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151172</t>
+          <t>151358</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>228336</t>
+          <t>228399</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>271120</t>
+          <t>274008</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>239245</t>
+          <t>238786</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>275693</t>
+          <t>273811</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>206413</t>
+          <t>206346</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>243271</t>
+          <t>243816</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>457611</t>
+          <t>452774</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>509599</t>
+          <t>506770</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27334</t>
+          <t>26754</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>2272</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8702</t>
+          <t>8657</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2528</t>
+          <t>2575</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>9228</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15322</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4799</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4542,7 +4542,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10963</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>8402</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3696</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6797</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>16531</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17755</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5743</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13583</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29174</t>
+          <t>29206</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,49%</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>616</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>5669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1222</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>7514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13383</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27063</t>
+          <t>27563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25111</t>
+          <t>24857</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41482</t>
+          <t>42767</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43353</t>
+          <t>42672</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65721</t>
+          <t>64013</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10110</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>22731</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18021</t>
+          <t>18132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32972</t>
+          <t>33363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31824</t>
+          <t>31715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50942</t>
+          <t>51356</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20492</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>36732</t>
+          <t>35902</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33343</t>
+          <t>33746</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51396</t>
+          <t>50769</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58134</t>
+          <t>57467</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>81366</t>
+          <t>81331</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82524</t>
+          <t>81672</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102491</t>
+          <t>101590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>77969</t>
+          <t>77342</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100543</t>
+          <t>98843</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,14%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165131</t>
+          <t>164803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195382</t>
+          <t>195495</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,73%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>5054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>14684</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6835</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18604</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,7 +5558,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13721</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28541</t>
+          <t>28303</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8589</t>
+          <t>8537</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6563</t>
+          <t>6605</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9483</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22450</t>
+          <t>22232</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6362</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17107</t>
+          <t>17946</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21177</t>
+          <t>21190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37465</t>
+          <t>37022</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>30122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>48630</t>
+          <t>50807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>34400</t>
+          <t>34992</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>30481</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>48838</t>
+          <t>49332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>69665</t>
+          <t>69565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95687</t>
+          <t>94194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,68%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>81630</t>
+          <t>81307</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>101602</t>
+          <t>101303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,08%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56673</t>
+          <t>57982</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>77052</t>
+          <t>77730</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>50,28%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>144337</t>
+          <t>145535</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>173932</t>
+          <t>173693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,58%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1379</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>8788</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4091</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>12480</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7471</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18647</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3537</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14142</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13829</t>
+          <t>13317</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10299</t>
+          <t>10295</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23273</t>
+          <t>23968</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>19683</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35626</t>
+          <t>35345</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30409</t>
+          <t>29461</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>48827</t>
+          <t>48330</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>53650</t>
+          <t>53593</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>77536</t>
+          <t>76732</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>91069</t>
+          <t>91580</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>109140</t>
+          <t>109773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>78946</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98640</t>
+          <t>98903</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>176716</t>
+          <t>176916</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>202861</t>
+          <t>203293</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,84%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10924</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>16867</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22507</t>
+          <t>23316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64485</t>
+          <t>65191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93991</t>
+          <t>93129</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52271</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76235</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>87414</t>
+          <t>86894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>118821</t>
+          <t>116293</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87388</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116286</t>
+          <t>118264</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109532</t>
+          <t>108368</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141471</t>
+          <t>141606</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>204838</t>
+          <t>207218</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>248558</t>
+          <t>249326</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282753</t>
+          <t>281515</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>315904</t>
+          <t>317666</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>236539</t>
+          <t>235991</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>273474</t>
+          <t>273740</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>527949</t>
+          <t>527304</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>580503</t>
+          <t>580139</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>62772</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3351</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>4880</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8134,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2858</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8149,7 +8149,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3898</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8219,7 +8219,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>503</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5240</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1563</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9577</t>
+          <t>9757</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>42,37%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8576</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,87%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,7%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>13216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,39%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1426</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8523,7 +8523,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1866</t>
+          <t>2034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8956</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3737</t>
+          <t>3901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>16812</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19712</t>
+          <t>19079</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>14926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29448</t>
+          <t>30673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,97%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4740</t>
+          <t>4670</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13139</t>
+          <t>13034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19263</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14832</t>
+          <t>14502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28922</t>
+          <t>28667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15037</t>
+          <t>14753</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>21943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8979,7 +8979,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>16910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32956</t>
+          <t>33057</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,68%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24195</t>
+          <t>24384</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36765</t>
+          <t>37024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,32%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>45840</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>58536</t>
+          <t>58888</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78185</t>
+          <t>77553</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,54%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5563</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10025</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,06%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3419</t>
+          <t>3833</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>3423</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12845</t>
+          <t>12378</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10605</t>
+          <t>11575</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24255</t>
+          <t>24737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16935</t>
+          <t>16692</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32924</t>
+          <t>33069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>13721</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28534</t>
+          <t>29207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>26830</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>30264</t>
+          <t>28985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51979</t>
+          <t>52330</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45406</t>
+          <t>46145</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>66,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>41934</t>
+          <t>42100</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59425</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,25%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77097</t>
+          <t>76545</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100514</t>
+          <t>100540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>60,88%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2258</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>554</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7907</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10102,7 +10102,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6776</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10117,7 +10117,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>1614</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11346</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>376</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>17778</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10230,7 +10230,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>19816</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,82%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>21703</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>19943</t>
+          <t>19934</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>43816</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28324</t>
+          <t>27266</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>60479</t>
+          <t>61056</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>93105</t>
+          <t>93444</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>114786</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64469</t>
+          <t>64242</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88793</t>
+          <t>88148</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,14%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>162651</t>
+          <t>163969</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203575</t>
+          <t>203112</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>961</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7476</t>
+          <t>7989</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5536</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7633</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>23236</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16619</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>32357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25380</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>46834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11397</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>51839</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43780</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>72849</t>
+          <t>72272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59920</t>
+          <t>58204</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54543</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86087</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>89999</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>132714</t>
+          <t>132785</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>162262</t>
+          <t>161272</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>205337</t>
+          <t>202826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>150833</t>
+          <t>152681</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>184544</t>
+          <t>185940</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>322935</t>
+          <t>323728</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>382799</t>
+          <t>384479</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>41172</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/IMC_inf_MED_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Edad-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,19 +735,19 @@
         <v>7396</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>4028</v>
+        <v>4020</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>11380</v>
+        <v>12078</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2809125662965085</v>
+        <v>0.213732149605259</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1529761884651679</v>
+        <v>0.1161642520070642</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.4322407050011723</v>
+        <v>0.3490359968846616</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>14</v>
@@ -756,19 +756,19 @@
         <v>9288</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>5279</v>
+        <v>5779</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>13668</v>
+        <v>14708</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.300028850880047</v>
+        <v>0.2254320690885943</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.1705411218831661</v>
+        <v>0.140275034503227</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.4414997725435031</v>
+        <v>0.356983556661046</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>25</v>
@@ -777,19 +777,19 @@
         <v>16684</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>11792</v>
+        <v>11564</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>22604</v>
+        <v>22844</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.2912431176568879</v>
+        <v>0.2200912746168553</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.2058532779806915</v>
+        <v>0.1525547428287214</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.3945841878371611</v>
+        <v>0.3013507275112669</v>
       </c>
     </row>
     <row r="5">
@@ -806,61 +806,61 @@
         <v>1901</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>5181</v>
+        <v>4716</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.07218752748751552</v>
+        <v>0.05492383494268471</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.02210283347653759</v>
+        <v>0.01657658434149495</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1967723407278772</v>
+        <v>0.136275419448576</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>1818</v>
+        <v>4341</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>572</v>
+        <v>1780</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>4940</v>
+        <v>8712</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.05873614060264207</v>
+        <v>0.1053710021230029</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.01848308474840232</v>
+        <v>0.04321033186668238</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1595636085071581</v>
+        <v>0.2114543883282755</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>3719</v>
+        <v>6242</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>1287</v>
+        <v>3066</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>7806</v>
+        <v>10830</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.06491831978790945</v>
+        <v>0.08234281359783442</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.02246821040523178</v>
+        <v>0.04045253789485578</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1362629970433681</v>
+        <v>0.1428635002861644</v>
       </c>
     </row>
     <row r="6">
@@ -871,67 +871,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>4928</v>
+        <v>5815</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>2094</v>
+        <v>2619</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>9325</v>
+        <v>10665</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.1871622639063084</v>
+        <v>0.1680493233189377</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.07952546243669827</v>
+        <v>0.07568154929317736</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.3541941880556544</v>
+        <v>0.3082154124038269</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>6945</v>
+        <v>9756</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>3894</v>
+        <v>5566</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>11476</v>
+        <v>14188</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2243362735092766</v>
+        <v>0.2367906349640213</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1257912568757646</v>
+        <v>0.1350928957105174</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3706964880815123</v>
+        <v>0.3443528195282264</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>11872</v>
+        <v>15571</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>7391</v>
+        <v>10301</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>17836</v>
+        <v>21756</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2072513148825318</v>
+        <v>0.205411511566029</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1290165943990031</v>
+        <v>0.1358853605849814</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3113481074153204</v>
+        <v>0.2870068605759903</v>
       </c>
     </row>
     <row r="7">
@@ -942,67 +942,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>10126</v>
+        <v>17514</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>6390</v>
+        <v>13150</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>14040</v>
+        <v>22445</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3846111567922358</v>
+        <v>0.5061347528195436</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2426952382154695</v>
+        <v>0.3800256466914799</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5332773417892039</v>
+        <v>0.6486556401493293</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>10387</v>
+        <v>15297</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>6624</v>
+        <v>10876</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>14696</v>
+        <v>20491</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.3355359882985758</v>
+        <v>0.3712729318705421</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.2139785043876373</v>
+        <v>0.2639652388900258</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.4747281236915253</v>
+        <v>0.4973451290325368</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>20513</v>
+        <v>32811</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>15358</v>
+        <v>26223</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>26544</v>
+        <v>39370</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.3580906503398683</v>
+        <v>0.4328348314031837</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.2681020864179195</v>
+        <v>0.3459263626665932</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4633600920309123</v>
+        <v>0.5193616357039021</v>
       </c>
     </row>
     <row r="8">
@@ -1022,16 +1022,16 @@
         <v>630</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>4711</v>
+        <v>5134</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.07512648551743184</v>
+        <v>0.05715993931357508</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.02394536200563522</v>
+        <v>0.01821350695025955</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1789314214405161</v>
+        <v>0.1483675153908486</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>4</v>
@@ -1040,19 +1040,19 @@
         <v>2519</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>5684</v>
+        <v>5834</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.08136274670945848</v>
+        <v>0.06113336195383945</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.021246972413814</v>
+        <v>0.01555173251906284</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1836060120514242</v>
+        <v>0.1416096965227333</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>7</v>
@@ -1061,19 +1061,19 @@
         <v>4497</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>8785</v>
+        <v>8335</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.07849659733280254</v>
+        <v>0.05931956881609753</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.03405359611901804</v>
+        <v>0.02574545178269705</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.1533519856376115</v>
+        <v>0.1099598911836131</v>
       </c>
     </row>
     <row r="9">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>26328</v>
+        <v>34603</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1105,16 +1105,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>30957</v>
+        <v>41201</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1126,16 +1126,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>57285</v>
+        <v>75804</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1165,19 +1165,19 @@
         <v>59329</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>48587</v>
+        <v>47689</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>70215</v>
+        <v>71291</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2843827631053176</v>
+        <v>0.2307260852447379</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.2328945262052431</v>
+        <v>0.1854576858985607</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.3365635879701804</v>
+        <v>0.2772461047669819</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>51</v>
@@ -1186,19 +1186,19 @@
         <v>35059</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>26622</v>
+        <v>26475</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>43552</v>
+        <v>45197</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1861221156725733</v>
+        <v>0.1541568504657232</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.1413301288761683</v>
+        <v>0.1164129426953284</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.2312071076173958</v>
+        <v>0.1987325888948674</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>132</v>
@@ -1207,19 +1207,19 @@
         <v>94388</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>81650</v>
+        <v>78571</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>109959</v>
+        <v>108180</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.2377594290651079</v>
+        <v>0.1947892100643186</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.2056727722150251</v>
+        <v>0.1621471366198222</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.2769820262435513</v>
+        <v>0.2232516378488791</v>
       </c>
     </row>
     <row r="11">
@@ -1230,67 +1230,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>32744</v>
+        <v>41699</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>24816</v>
+        <v>32215</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>42291</v>
+        <v>51926</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1569528739879621</v>
+        <v>0.1621644260585353</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.1189517924235226</v>
+        <v>0.125281069159764</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.2027125450011329</v>
+        <v>0.2019379169016753</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>25837</v>
+        <v>32627</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>19126</v>
+        <v>24195</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>34048</v>
+        <v>42373</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1371616177802741</v>
+        <v>0.1434634624517261</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.1015379186077782</v>
+        <v>0.1063866046851166</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1807548942783445</v>
+        <v>0.1863182985378047</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>83</v>
+        <v>103</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>58581</v>
+        <v>74326</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>46976</v>
+        <v>60950</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>70544</v>
+        <v>88897</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1475621934525221</v>
+        <v>0.1533873474207368</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.118329893635519</v>
+        <v>0.1257816653384601</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.177697595485436</v>
+        <v>0.183457301386029</v>
       </c>
     </row>
     <row r="12">
@@ -1301,67 +1301,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>39122</v>
+        <v>52439</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>30332</v>
+        <v>41655</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>49697</v>
+        <v>63371</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.1875244732755621</v>
+        <v>0.203930352708827</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1453883697319775</v>
+        <v>0.1619940779103839</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2382109465924742</v>
+        <v>0.2464449357488499</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>35399</v>
+        <v>48131</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>26854</v>
+        <v>38732</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>44064</v>
+        <v>58110</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1879270429841866</v>
+        <v>0.2116324389422429</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1425646800835787</v>
+        <v>0.17030572366827</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2339253375498513</v>
+        <v>0.2555144907253939</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>74521</v>
+        <v>100569</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>61884</v>
+        <v>85264</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>87361</v>
+        <v>117017</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.1877154870994076</v>
+        <v>0.2075452368381765</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1558823957184401</v>
+        <v>0.1759597716224102</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.220057368739012</v>
+        <v>0.2414883968315017</v>
       </c>
     </row>
     <row r="13">
@@ -1372,67 +1372,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>67471</v>
+        <v>93716</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>56531</v>
+        <v>81359</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>79647</v>
+        <v>107896</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.32340864621605</v>
+        <v>0.3644537124890321</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.2709706622494089</v>
+        <v>0.3164009729508937</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.3817713146719141</v>
+        <v>0.4196010887900077</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>84274</v>
+        <v>103811</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>73697</v>
+        <v>92091</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>95716</v>
+        <v>116360</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.4473961254665491</v>
+        <v>0.4564631459501742</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.3912431865773474</v>
+        <v>0.4049285486741461</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5081360053562616</v>
+        <v>0.5116419511915442</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>215</v>
+        <v>280</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>151745</v>
+        <v>197527</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>135535</v>
+        <v>179901</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>167833</v>
+        <v>214664</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.3822390102827661</v>
+        <v>0.4076372644111205</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.3414059889983515</v>
+        <v>0.3712618905728782</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.4227649921964711</v>
+        <v>0.4430026343659476</v>
       </c>
     </row>
     <row r="14">
@@ -1449,19 +1449,19 @@
         <v>9958</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>5330</v>
+        <v>5858</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>16267</v>
+        <v>17297</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.04773124341510821</v>
+        <v>0.03872542349886771</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.02554669097077645</v>
+        <v>0.02278178129796676</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.07797315353809064</v>
+        <v>0.06726734742823313</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>12</v>
@@ -1470,19 +1470,19 @@
         <v>7797</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4076</v>
+        <v>4233</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>13301</v>
+        <v>12895</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.04139309809641695</v>
+        <v>0.03428410219013357</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.02163847337931222</v>
+        <v>0.01861182268762415</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.07061250132396978</v>
+        <v>0.05670137400835654</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>26</v>
@@ -1491,19 +1491,19 @@
         <v>17755</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>12200</v>
+        <v>11913</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>26052</v>
+        <v>26173</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.04472388010019625</v>
+        <v>0.0366409412656476</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.0307300935928547</v>
+        <v>0.02458575515055863</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.06562406022813115</v>
+        <v>0.05401378772410216</v>
       </c>
     </row>
     <row r="15">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>208624</v>
+        <v>257140</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1535,16 +1535,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>270</v>
+        <v>326</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>188366</v>
+        <v>227425</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>561</v>
+        <v>684</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>396990</v>
+        <v>484566</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1595,19 +1595,19 @@
         <v>14952</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>9740</v>
+        <v>9850</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>22626</v>
+        <v>22282</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.1116392799256651</v>
+        <v>0.09476172471494608</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.07272324286070898</v>
+        <v>0.06242712646710371</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1689353966036589</v>
+        <v>0.1412170270307287</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>14</v>
@@ -1616,19 +1616,19 @@
         <v>9191</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>5213</v>
+        <v>4974</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>15251</v>
+        <v>14551</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.06965732408794396</v>
+        <v>0.05883093318168549</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.03951199969437911</v>
+        <v>0.03183726369952485</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1155841386329666</v>
+        <v>0.09314222942731334</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>35</v>
@@ -1637,19 +1637,19 @@
         <v>24143</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>17442</v>
+        <v>17084</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>32044</v>
+        <v>32564</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.09080514134135174</v>
+        <v>0.07688553626016273</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.06560292631035562</v>
+        <v>0.05440759501735477</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.1205215034925394</v>
+        <v>0.1037042747770902</v>
       </c>
     </row>
     <row r="17">
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>18082</v>
+        <v>23459</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>12278</v>
+        <v>16265</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>25322</v>
+        <v>31666</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1350141111951251</v>
+        <v>0.1486792981418846</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.09167114809546552</v>
+        <v>0.1030843945363289</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1890659250166228</v>
+        <v>0.2006938168332005</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>20066</v>
+        <v>24280</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>14677</v>
+        <v>16686</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>28302</v>
+        <v>31553</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1520822422906866</v>
+        <v>0.1554147169290783</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.1112358066135761</v>
+        <v>0.1068101119865023</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.2145038397145503</v>
+        <v>0.2019728449082607</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>38149</v>
+        <v>47739</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>29168</v>
+        <v>37400</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>48284</v>
+        <v>58353</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1434844123405674</v>
+        <v>0.1520302851483998</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.109705597707209</v>
+        <v>0.1191056076518638</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1816035817086938</v>
+        <v>0.1858309790065143</v>
       </c>
     </row>
     <row r="18">
@@ -1731,67 +1731,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>38574</v>
+        <v>47440</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>30722</v>
+        <v>37982</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>47772</v>
+        <v>56972</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2880141878669307</v>
+        <v>0.3006612049955436</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.2293889302297077</v>
+        <v>0.2407205563912473</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3566905487276247</v>
+        <v>0.3610777853378474</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>41524</v>
+        <v>46205</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>32917</v>
+        <v>37620</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>50310</v>
+        <v>56130</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.3147094045245815</v>
+        <v>0.2957607981030922</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2494739021804727</v>
+        <v>0.2408076399319223</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.381298185017922</v>
+        <v>0.3592868767684871</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>80098</v>
+        <v>93645</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>67864</v>
+        <v>80695</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>91992</v>
+        <v>107629</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.3012620662062253</v>
+        <v>0.2982231680535105</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.2552494806327264</v>
+        <v>0.2569816128312614</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.3459996623747237</v>
+        <v>0.3427574713063589</v>
       </c>
     </row>
     <row r="19">
@@ -1802,67 +1802,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>59112</v>
+        <v>68723</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>50235</v>
+        <v>59139</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>68352</v>
+        <v>79209</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.44136488440218</v>
+        <v>0.4355536324518674</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.3750830909986254</v>
+        <v>0.3748095058979716</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5103569763774749</v>
+        <v>0.5020085782628111</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>57945</v>
+        <v>73332</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>48502</v>
+        <v>63155</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>68109</v>
+        <v>83500</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.4391657434085036</v>
+        <v>0.4693983145770238</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.3675957424497621</v>
+        <v>0.4042546219319674</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.5161981124855057</v>
+        <v>0.5344851638958433</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>117057</v>
+        <v>142055</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>104353</v>
+        <v>127545</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>130390</v>
+        <v>155418</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.4402735296209544</v>
+        <v>0.4523919454988116</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.3924918379681944</v>
+        <v>0.4061832184638544</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.4904204810211287</v>
+        <v>0.4949485013975257</v>
       </c>
     </row>
     <row r="20">
@@ -1879,19 +1879,19 @@
         <v>3210</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>786</v>
+        <v>816</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>7888</v>
+        <v>8113</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02396753661009902</v>
+        <v>0.0203441396957583</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.005867301820219571</v>
+        <v>0.005174248399342734</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.05889897301148846</v>
+        <v>0.05142110881713782</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>5</v>
@@ -1900,19 +1900,19 @@
         <v>3217</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1136</v>
+        <v>1321</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>7700</v>
+        <v>7312</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.02438528568828436</v>
+        <v>0.0205952372091202</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.008613184775104891</v>
+        <v>0.00845682764755748</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05835435965977297</v>
+        <v>0.04680408517258514</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>9</v>
@@ -1921,19 +1921,19 @@
         <v>6427</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>3005</v>
+        <v>3072</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>11297</v>
+        <v>11729</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.02417485049090118</v>
+        <v>0.0204690650391154</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01130395461026383</v>
+        <v>0.009782151187656921</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.04249043446787714</v>
+        <v>0.03735358261468164</v>
       </c>
     </row>
     <row r="21">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>133930</v>
+        <v>157784</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1965,16 +1965,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>131944</v>
+        <v>156225</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1986,16 +1986,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>382</v>
+        <v>449</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>265874</v>
+        <v>314009</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2025,19 +2025,19 @@
         <v>1897</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>5171</v>
+        <v>5764</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01228915702931849</v>
+        <v>0.01075690855220854</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.003998027358655306</v>
+        <v>0.003506692624489566</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.03350073473088241</v>
+        <v>0.03268897061945847</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>1</v>
@@ -2049,16 +2049,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>3841</v>
+        <v>4661</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.005139783587008504</v>
+        <v>0.004481801607241548</v>
       </c>
       <c r="O22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.025710109987619</v>
+        <v>0.02720421791902776</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>4</v>
@@ -2067,19 +2067,19 @@
         <v>2665</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>6565</v>
+        <v>6659</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.008772715673620314</v>
+        <v>0.007664491668346041</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.002147998770676895</v>
+        <v>0.00189587280675186</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.0216131485113526</v>
+        <v>0.01915384672329436</v>
       </c>
     </row>
     <row r="23">
@@ -2090,67 +2090,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>10579</v>
+        <v>11151</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>6391</v>
+        <v>6870</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>16271</v>
+        <v>17583</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.06853809219740951</v>
+        <v>0.06323472586694008</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.04140742536302613</v>
+        <v>0.03895798073038476</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.105414334524493</v>
+        <v>0.09970889087563461</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>7180</v>
+        <v>9782</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>3332</v>
+        <v>5450</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>12770</v>
+        <v>16495</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.04805654061927443</v>
+        <v>0.05709110419653832</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.02230205523668437</v>
+        <v>0.03180808852987557</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.0854767356636965</v>
+        <v>0.09627402556869646</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>17759</v>
+        <v>20933</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>11880</v>
+        <v>14052</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>25174</v>
+        <v>29489</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.05846417794752682</v>
+        <v>0.06020710585213667</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.03911086571001736</v>
+        <v>0.04041673992559438</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.08287557886433877</v>
+        <v>0.08481653471723925</v>
       </c>
     </row>
     <row r="24">
@@ -2161,67 +2161,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>51413</v>
+        <v>57603</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>42267</v>
+        <v>47690</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>61555</v>
+        <v>67377</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.3330905516333731</v>
+        <v>0.3266621185943741</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.2738366036264521</v>
+        <v>0.2704444480040448</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.398793509521823</v>
+        <v>0.3820866493083666</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>32439</v>
+        <v>37724</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>24444</v>
+        <v>28653</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>41235</v>
+        <v>46659</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2171263540237074</v>
+        <v>0.2201728494577817</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1636094990031998</v>
+        <v>0.1672315456198419</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2759979565791818</v>
+        <v>0.2723238466385753</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>83853</v>
+        <v>95327</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>71247</v>
+        <v>81976</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>95862</v>
+        <v>109237</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2760532037391178</v>
+        <v>0.2741834570008372</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.2345526534309645</v>
+        <v>0.235783638221319</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.3155891359351579</v>
+        <v>0.3141919321057116</v>
       </c>
     </row>
     <row r="25">
@@ -2232,67 +2232,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>87880</v>
+        <v>103105</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>77291</v>
+        <v>92398</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>97535</v>
+        <v>113019</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.5693483601852797</v>
+        <v>0.5846988326086821</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.5007462680292837</v>
+        <v>0.523981934594188</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.6319014533307581</v>
+        <v>0.6409184111748915</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>104999</v>
+        <v>119046</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>95388</v>
+        <v>108514</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>114204</v>
+        <v>128351</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.7027900525262909</v>
+        <v>0.6948090150958084</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6384626579743732</v>
+        <v>0.6333343464449671</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.7644045605020483</v>
+        <v>0.7491129642867046</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>277</v>
+        <v>320</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>192879</v>
+        <v>222151</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>179162</v>
+        <v>207372</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>207039</v>
+        <v>237102</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.634982067713456</v>
+        <v>0.6389619057952637</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5898249138791674</v>
+        <v>0.596452833367648</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.6815977805717763</v>
+        <v>0.6819657374494524</v>
       </c>
     </row>
     <row r="26">
@@ -2309,19 +2309,19 @@
         <v>2583</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>5834</v>
+        <v>6189</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01673383895461918</v>
+        <v>0.01464741437779528</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.00413846998588823</v>
+        <v>0.003685107047310527</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.03779350750731405</v>
+        <v>0.0350969928333176</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>6</v>
@@ -2330,19 +2330,19 @@
         <v>4017</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1842</v>
+        <v>1423</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>8627</v>
+        <v>8234</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.02688726924371873</v>
+        <v>0.02344522964262999</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.01232823248362592</v>
+        <v>0.008307554916479725</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.05774496781177332</v>
+        <v>0.04805521872069731</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>10</v>
@@ -2351,19 +2351,19 @@
         <v>6600</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>3200</v>
+        <v>3202</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>11298</v>
+        <v>11007</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.02172783492627905</v>
+        <v>0.01898303968341646</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.01053416527044628</v>
+        <v>0.00920927704191352</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.03719457855195878</v>
+        <v>0.03165940755697503</v>
       </c>
     </row>
     <row r="27">
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>154352</v>
+        <v>176339</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2395,16 +2395,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>149403</v>
+        <v>171337</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -2416,16 +2416,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>440</v>
+        <v>503</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>303755</v>
+        <v>347675</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -2455,19 +2455,19 @@
         <v>83574</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>70758</v>
+        <v>71225</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>99010</v>
+        <v>99227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.1597250072999284</v>
+        <v>0.1335326383457107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.1352310964520681</v>
+        <v>0.1138016460046284</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1892277508849157</v>
+        <v>0.158543575909549</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>80</v>
@@ -2476,19 +2476,19 @@
         <v>54306</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>44362</v>
+        <v>43336</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>67459</v>
+        <v>65959</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1084664916291259</v>
+        <v>0.09108860998299645</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.08860513025758981</v>
+        <v>0.07268877310993178</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1347370218607096</v>
+        <v>0.1106342565805754</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>196</v>
@@ -2497,19 +2497,19 @@
         <v>137879</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>120549</v>
+        <v>120328</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>157141</v>
+        <v>157805</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.1346605456582088</v>
+        <v>0.1128260123870841</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.1177350154829054</v>
+        <v>0.09846397032856438</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1534719792042908</v>
+        <v>0.1291311835642532</v>
       </c>
     </row>
     <row r="29">
@@ -2520,67 +2520,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>63306</v>
+        <v>78209</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50655</v>
+        <v>65450</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>76045</v>
+        <v>93184</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1209900700982077</v>
+        <v>0.1249620234729365</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09681205943232604</v>
+        <v>0.1045750566185443</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1453359427475905</v>
+        <v>0.1488887874087832</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>54901</v>
+        <v>71030</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>43747</v>
+        <v>58829</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>66882</v>
+        <v>86348</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1096550973152521</v>
+        <v>0.1191403589241443</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.08737726512906233</v>
+        <v>0.09867476264798246</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1335852034172904</v>
+        <v>0.1448337675106713</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>118207</v>
+        <v>149240</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>101934</v>
+        <v>129995</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>135501</v>
+        <v>168877</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1154474790416712</v>
+        <v>0.1221218823525349</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.09955378330818683</v>
+        <v>0.1063739806341852</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1323380834695329</v>
+        <v>0.13819126841729</v>
       </c>
     </row>
     <row r="30">
@@ -2591,67 +2591,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>134037</v>
+        <v>163296</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>118593</v>
+        <v>146696</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>150566</v>
+        <v>182431</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2561696973185351</v>
+        <v>0.2609127000597699</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.226652974890583</v>
+        <v>0.2343887875967914</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2877598635714188</v>
+        <v>0.2914862564145228</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>116307</v>
+        <v>141815</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>102241</v>
+        <v>126567</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>132417</v>
+        <v>160317</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2323030171496264</v>
+        <v>0.237870412302293</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2042080616132547</v>
+        <v>0.2122944254963693</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2644795750005397</v>
+        <v>0.2689039442236753</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>250344</v>
+        <v>305112</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>228000</v>
+        <v>280777</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>274451</v>
+        <v>329367</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.244499334223149</v>
+        <v>0.249671353462135</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.2226775305922569</v>
+        <v>0.2297584387082437</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2680433185906281</v>
+        <v>0.2695192623160355</v>
       </c>
     </row>
     <row r="31">
@@ -2662,67 +2662,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>224589</v>
+        <v>283058</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>205397</v>
+        <v>262180</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>242386</v>
+        <v>303916</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4292323533280058</v>
+        <v>0.4522660199957924</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.3925537144296473</v>
+        <v>0.4189075394729864</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.4632455520061621</v>
+        <v>0.4855930397726698</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>369</v>
+        <v>446</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>257606</v>
+        <v>311486</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>240625</v>
+        <v>290995</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>276260</v>
+        <v>331750</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.5145216830855965</v>
+        <v>0.5224630132644862</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.480606662493651</v>
+        <v>0.4880927559959314</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.5517803847176144</v>
+        <v>0.5564513623275738</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>693</v>
+        <v>855</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>482195</v>
+        <v>594544</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>456249</v>
+        <v>566064</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>507772</v>
+        <v>622981</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.4709372506739659</v>
+        <v>0.486512130440671</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.4455972751771586</v>
+        <v>0.4632068362608711</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.4959176594829832</v>
+        <v>0.5097815840109283</v>
       </c>
     </row>
     <row r="32">
@@ -2739,19 +2739,19 @@
         <v>17729</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>11540</v>
+        <v>11734</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>26157</v>
+        <v>25977</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.03388287195532295</v>
+        <v>0.02832661812579045</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.02205505524700879</v>
+        <v>0.01874903936099447</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.04999061100541763</v>
+        <v>0.04150608855043674</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>27</v>
@@ -2760,19 +2760,19 @@
         <v>17550</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>11218</v>
+        <v>11728</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>24693</v>
+        <v>24750</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.0350537108203991</v>
+        <v>0.02943760552608009</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02240678910564161</v>
+        <v>0.01967173660685467</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.04931933223154731</v>
+        <v>0.04151435620132864</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>52</v>
@@ -2781,19 +2781,19 @@
         <v>35279</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>26343</v>
+        <v>26212</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>45413</v>
+        <v>46083</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.03445539040300503</v>
+        <v>0.02886862135757496</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.02572817312631482</v>
+        <v>0.02144903448420012</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.04435299021328579</v>
+        <v>0.03770962350672428</v>
       </c>
     </row>
     <row r="33">
@@ -2804,16 +2804,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -2825,16 +2825,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -2846,16 +2846,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -2927,7 +2927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3117,19 +3117,19 @@
         <v>5277</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>2591</v>
+        <v>2620</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9191</v>
+        <v>9653</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.2057386781444216</v>
+        <v>0.1714550973156936</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1010209906651569</v>
+        <v>0.08513292776756404</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.3583246832552536</v>
+        <v>0.3136054446728603</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>8</v>
@@ -3138,19 +3138,19 @@
         <v>4925</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2337</v>
+        <v>2391</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>8908</v>
+        <v>8773</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1762261354846482</v>
+        <v>0.1546031196028831</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.08361672377547819</v>
+        <v>0.07506566200663474</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.3187479858655756</v>
+        <v>0.2754054943895872</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>16</v>
@@ -3159,19 +3159,19 @@
         <v>10202</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>6306</v>
+        <v>6092</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>15056</v>
+        <v>15757</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1903500427010384</v>
+        <v>0.1628842728801811</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1176585057424745</v>
+        <v>0.09726542918754023</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2809005897934721</v>
+        <v>0.2515686080510099</v>
       </c>
     </row>
     <row r="5">
@@ -3182,67 +3182,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>1988</v>
+        <v>2640</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>643</v>
+        <v>662</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>5259</v>
+        <v>5906</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.07748875147497949</v>
+        <v>0.08577170351304263</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.0250839655444953</v>
+        <v>0.02150751903887812</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.2050048098686335</v>
+        <v>0.1918935238452741</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>3866</v>
+        <v>5310</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>1460</v>
+        <v>2652</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>7676</v>
+        <v>9079</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1383141234648263</v>
+        <v>0.1666744624303181</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.05224943744782811</v>
+        <v>0.08325201097482723</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.2746604844375282</v>
+        <v>0.2850065865163872</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>5853</v>
+        <v>7950</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>2777</v>
+        <v>4221</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>10572</v>
+        <v>12784</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.109204740369957</v>
+        <v>0.1269184077661258</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.05181834666981257</v>
+        <v>0.06738368285936386</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1972413743744989</v>
+        <v>0.2040977273619584</v>
       </c>
     </row>
     <row r="6">
@@ -3253,67 +3253,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>6614</v>
+        <v>7713</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3837</v>
+        <v>4263</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>10780</v>
+        <v>11778</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2578579708563055</v>
+        <v>0.2505915676320727</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.1495921949403719</v>
+        <v>0.1385011230440499</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.4202716109556942</v>
+        <v>0.3826633109942809</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>4378</v>
+        <v>4975</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>1971</v>
+        <v>2546</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>8451</v>
+        <v>8927</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.1566412146509704</v>
+        <v>0.1561594726347227</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.07052456060598956</v>
+        <v>0.0799148342439904</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3023864925455617</v>
+        <v>0.2802234577384181</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>10992</v>
+        <v>12688</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>6691</v>
+        <v>7978</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>16439</v>
+        <v>18382</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2050808252215873</v>
+        <v>0.2025639164511275</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1248331029360989</v>
+        <v>0.1273653739251724</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3067125019658088</v>
+        <v>0.2934667706248147</v>
       </c>
     </row>
     <row r="7">
@@ -3324,67 +3324,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>9623</v>
+        <v>13001</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>5916</v>
+        <v>8856</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>13871</v>
+        <v>17632</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3751545846398763</v>
+        <v>0.4223790954643228</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.230628815166203</v>
+        <v>0.2877191575827205</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5407458614960367</v>
+        <v>0.5728388767587206</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>13558</v>
+        <v>15426</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>8998</v>
+        <v>10904</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>17790</v>
+        <v>19643</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4851206071971579</v>
+        <v>0.4842267779397323</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.3219543828242217</v>
+        <v>0.3422908884527908</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.6365343624821634</v>
+        <v>0.6166038232478759</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>23181</v>
+        <v>28426</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>17739</v>
+        <v>22369</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>29023</v>
+        <v>34936</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4324938336432982</v>
+        <v>0.4538344912210535</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.330965806958924</v>
+        <v>0.3571236123042811</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5414957210593623</v>
+        <v>0.5577559824736371</v>
       </c>
     </row>
     <row r="8">
@@ -3401,19 +3401,19 @@
         <v>2149</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>613</v>
+        <v>620</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>5782</v>
+        <v>5740</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.08376001488441709</v>
+        <v>0.06980253607486818</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.02390406153095554</v>
+        <v>0.02013260151784699</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.2254060479330712</v>
+        <v>0.1864814571331632</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>2</v>
@@ -3425,16 +3425,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>4392</v>
+        <v>4196</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.04369791920239711</v>
+        <v>0.03833616739234377</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.1571491331633273</v>
+        <v>0.1317321735311878</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>5</v>
@@ -3443,19 +3443,19 @@
         <v>3370</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1291</v>
+        <v>1239</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>7509</v>
+        <v>7660</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.06287055806411902</v>
+        <v>0.05379891168151217</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.02407927792346566</v>
+        <v>0.01977941854263993</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.1401074131568436</v>
+        <v>0.1222909283928439</v>
       </c>
     </row>
     <row r="9">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>25651</v>
+        <v>30780</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3487,16 +3487,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>27948</v>
+        <v>31856</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3508,16 +3508,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>53598</v>
+        <v>62636</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3547,19 +3547,19 @@
         <v>32891</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>24805</v>
+        <v>24988</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>42889</v>
+        <v>43413</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1651164131171723</v>
+        <v>0.1308591018609692</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1245239507556586</v>
+        <v>0.09941625351022587</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.215308301552448</v>
+        <v>0.1727234775391246</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>32</v>
@@ -3568,19 +3568,19 @@
         <v>20301</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>14235</v>
+        <v>14437</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>27199</v>
+        <v>28412</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1233079846440783</v>
+        <v>0.1011843295830908</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.08646541113285361</v>
+        <v>0.07195585258167081</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1652115698580149</v>
+        <v>0.1416161406697568</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>79</v>
@@ -3589,19 +3589,19 @@
         <v>53191</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>43032</v>
+        <v>43542</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>64266</v>
+        <v>66696</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1461980632176945</v>
+        <v>0.117686548864747</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.1182756320187855</v>
+        <v>0.09633823281222414</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1766370778864301</v>
+        <v>0.1475658684615496</v>
       </c>
     </row>
     <row r="11">
@@ -3612,67 +3612,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>24587</v>
+        <v>32000</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>17860</v>
+        <v>24166</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>33589</v>
+        <v>41347</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1234307718855798</v>
+        <v>0.1273171159215891</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.08966111910381248</v>
+        <v>0.09614620996976589</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1686214287373681</v>
+        <v>0.1645024254986074</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>16241</v>
+        <v>18540</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>11038</v>
+        <v>12346</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>23327</v>
+        <v>25673</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.09864821662649954</v>
+        <v>0.09240847553917644</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.06704467859491663</v>
+        <v>0.06153582158237318</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1416910235553114</v>
+        <v>0.1279633966056962</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>40828</v>
+        <v>50540</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>32504</v>
+        <v>40724</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>51310</v>
+        <v>63230</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1122166442821911</v>
+        <v>0.1118212627046738</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.08933893630792937</v>
+        <v>0.09010211454323996</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1410257480899554</v>
+        <v>0.1398960461870711</v>
       </c>
     </row>
     <row r="12">
@@ -3683,67 +3683,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>41394</v>
+        <v>55409</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>33250</v>
+        <v>46132</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>50854</v>
+        <v>65528</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2078029456205483</v>
+        <v>0.2204525201144605</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1669178419887445</v>
+        <v>0.1835398475859053</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2552935931085913</v>
+        <v>0.2607102550321844</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>27704</v>
+        <v>39135</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>20503</v>
+        <v>30454</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>36095</v>
+        <v>48649</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1682764883066404</v>
+        <v>0.1950594141153994</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1245369141854517</v>
+        <v>0.1517900074282417</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2192421140154304</v>
+        <v>0.2424805882455968</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>69098</v>
+        <v>94544</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>57209</v>
+        <v>80988</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>81050</v>
+        <v>110460</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.1899171896363807</v>
+        <v>0.2091805874647642</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1572413685468262</v>
+        <v>0.179186180221042</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2227692320988202</v>
+        <v>0.2443934921470271</v>
       </c>
     </row>
     <row r="13">
@@ -3754,67 +3754,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>131</v>
+        <v>174</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>88576</v>
+        <v>119294</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>77726</v>
+        <v>105503</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>100288</v>
+        <v>132135</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4446656150092625</v>
+        <v>0.4746246885507544</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3901943229297486</v>
+        <v>0.4197572351178105</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5034614878999428</v>
+        <v>0.5257143429409821</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>91792</v>
+        <v>114059</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>81530</v>
+        <v>103975</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>101394</v>
+        <v>126090</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5575547704744395</v>
+        <v>0.5685031031386361</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4952226219951467</v>
+        <v>0.5182412650846698</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.6158729077877609</v>
+        <v>0.6284681243506025</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>277</v>
+        <v>356</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>180369</v>
+        <v>233353</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>165103</v>
+        <v>216158</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>194999</v>
+        <v>248927</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.4957480551043547</v>
+        <v>0.5162970687051944</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4537905137044065</v>
+        <v>0.4782525878755959</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5359598806682799</v>
+        <v>0.5507530420882168</v>
       </c>
     </row>
     <row r="14">
@@ -3831,19 +3831,19 @@
         <v>11749</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>7155</v>
+        <v>7056</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>18183</v>
+        <v>19140</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.05898425436743709</v>
+        <v>0.04674657355222683</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.03592045927277108</v>
+        <v>0.02807457506128585</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.09127953434142838</v>
+        <v>0.0761519567294331</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>14</v>
@@ -3852,19 +3852,19 @@
         <v>8596</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4688</v>
+        <v>4646</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>13692</v>
+        <v>13620</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.05221253994834229</v>
+        <v>0.04284467762369738</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.02847576392223845</v>
+        <v>0.02315463026581511</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.08316798353483909</v>
+        <v>0.06788501756768764</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>30</v>
@@ -3873,19 +3873,19 @@
         <v>20345</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>13629</v>
+        <v>14379</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>28058</v>
+        <v>29364</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.05592004775937909</v>
+        <v>0.04501453226062058</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.03746018257148902</v>
+        <v>0.03181469651723666</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.07711907155258381</v>
+        <v>0.06496760002782795</v>
       </c>
     </row>
     <row r="15">
@@ -3896,16 +3896,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>295</v>
+        <v>370</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>199197</v>
+        <v>251344</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3917,16 +3917,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>164634</v>
+        <v>200630</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3938,16 +3938,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>555</v>
+        <v>688</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>363831</v>
+        <v>451975</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3977,19 +3977,19 @@
         <v>11025</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>6551</v>
+        <v>6514</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>17149</v>
+        <v>16948</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.07194021579000337</v>
+        <v>0.06119047459563749</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.04274675358105628</v>
+        <v>0.03615114360328518</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1119000376101622</v>
+        <v>0.0940622177827533</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>5</v>
@@ -3998,19 +3998,19 @@
         <v>3722</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>1421</v>
+        <v>1403</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>8349</v>
+        <v>8290</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.02420468102654579</v>
+        <v>0.02030968518168642</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.009242683486176267</v>
+        <v>0.007654810033908084</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.05430002640001722</v>
+        <v>0.04524069273058726</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>21</v>
@@ -4019,19 +4019,19 @@
         <v>14747</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>9961</v>
+        <v>9340</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>22409</v>
+        <v>22680</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.04803363820229161</v>
+        <v>0.04057780852977094</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.03244365811973669</v>
+        <v>0.02569946475634655</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.07299016921261713</v>
+        <v>0.06240509202007404</v>
       </c>
     </row>
     <row r="17">
@@ -4042,67 +4042,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>28291</v>
+        <v>32397</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>20386</v>
+        <v>24151</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>36556</v>
+        <v>42148</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1845974076183016</v>
+        <v>0.1798035560377529</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.1330174743281781</v>
+        <v>0.1340385973007476</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2385245698442927</v>
+        <v>0.2339176514572368</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>10746</v>
+        <v>13252</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>6368</v>
+        <v>8465</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>16545</v>
+        <v>19849</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.06988746571384953</v>
+        <v>0.07232035172318539</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.04141438392335214</v>
+        <v>0.04619583600494045</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1076040504774381</v>
+        <v>0.1083223617331952</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>39036</v>
+        <v>45649</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>30039</v>
+        <v>36164</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>49928</v>
+        <v>56812</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1271491745606929</v>
+        <v>0.1256090204139028</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.09784179522404074</v>
+        <v>0.09950925038073336</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1626245421249436</v>
+        <v>0.1563230631482939</v>
       </c>
     </row>
     <row r="18">
@@ -4113,67 +4113,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>38814</v>
+        <v>47401</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>30035</v>
+        <v>38168</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>48819</v>
+        <v>56787</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.2532622392792753</v>
+        <v>0.2630739046224896</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1959771352369061</v>
+        <v>0.2118314037414969</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.3185406585415385</v>
+        <v>0.315163690719887</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>43168</v>
+        <v>49760</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>34751</v>
+        <v>40885</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>52778</v>
+        <v>60820</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2807540970900314</v>
+        <v>0.2715480014872801</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.2260108012730301</v>
+        <v>0.2231186014522661</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3432610985383726</v>
+        <v>0.331905913138789</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>81982</v>
+        <v>97160</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>67986</v>
+        <v>83674</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>94534</v>
+        <v>112042</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2670305197654993</v>
+        <v>0.2673466628394365</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.2214431496711615</v>
+        <v>0.230238186007261</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.3079150477488727</v>
+        <v>0.3082959332330751</v>
       </c>
     </row>
     <row r="19">
@@ -4184,67 +4184,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>67473</v>
+        <v>81704</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>56861</v>
+        <v>70572</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>77287</v>
+        <v>92327</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.4402631421279914</v>
+        <v>0.4534569567442376</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.3710203278359086</v>
+        <v>0.3916718453333508</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5042951820276304</v>
+        <v>0.512414570673473</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>131</v>
+        <v>162</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>92039</v>
+        <v>112429</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>81360</v>
+        <v>100782</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>101869</v>
+        <v>122571</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5986060582812446</v>
+        <v>0.6135462957637432</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.5291480935803109</v>
+        <v>0.5499874873044455</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.6625337865182986</v>
+        <v>0.6688953378731216</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>227</v>
+        <v>278</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>159513</v>
+        <v>194133</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>144692</v>
+        <v>178731</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>173404</v>
+        <v>210084</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5195633370297589</v>
+        <v>0.5341762416019867</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4712893503515228</v>
+        <v>0.4917968649814073</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.5648099857153966</v>
+        <v>0.578066911892691</v>
       </c>
     </row>
     <row r="20">
@@ -4261,19 +4261,19 @@
         <v>7653</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4076</v>
+        <v>4038</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>13078</v>
+        <v>13148</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.04993699518442837</v>
+        <v>0.04247510799988237</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02659264097369012</v>
+        <v>0.02240813953056983</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.08533301627629167</v>
+        <v>0.07296831916540548</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>6</v>
@@ -4282,19 +4282,19 @@
         <v>4082</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>1400</v>
+        <v>1901</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>8242</v>
+        <v>8398</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.0265476978883287</v>
+        <v>0.02227566584410479</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.00910797120404822</v>
+        <v>0.01037260253867127</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.05360639251315304</v>
+        <v>0.0458282674866303</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>17</v>
@@ -4303,19 +4303,19 @@
         <v>11735</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>7498</v>
+        <v>6905</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>18529</v>
+        <v>17441</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.03822333044175728</v>
+        <v>0.03229026661490311</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.02442382922268521</v>
+        <v>0.01899891517748753</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.06035164746154321</v>
+        <v>0.04799010600260806</v>
       </c>
     </row>
     <row r="21">
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>214</v>
+        <v>252</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>153257</v>
+        <v>180181</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -4347,16 +4347,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>219</v>
+        <v>263</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>153756</v>
+        <v>183244</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -4368,16 +4368,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>433</v>
+        <v>515</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>307013</v>
+        <v>363425</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -4410,16 +4410,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>3525</v>
+        <v>3512</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.004788563195934387</v>
+        <v>0.004135384049775335</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.02412194977129862</v>
+        <v>0.02075635319204823</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>0</v>
@@ -4444,16 +4444,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>3492</v>
+        <v>4392</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.00243812323041183</v>
+        <v>0.002114134967939587</v>
       </c>
       <c r="V22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.01216759457685721</v>
+        <v>0.01326963893914191</v>
       </c>
     </row>
     <row r="23">
@@ -4464,25 +4464,25 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>7809</v>
+        <v>11051</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>3905</v>
+        <v>6104</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>13438</v>
+        <v>17785</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.05344242273128754</v>
+        <v>0.06531610836272438</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.0267248876693295</v>
+        <v>0.03607552601022374</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.09196666349384235</v>
+        <v>0.1051173090078479</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>11</v>
@@ -4491,40 +4491,40 @@
         <v>8014</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>4149</v>
+        <v>4003</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>13741</v>
+        <v>13595</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.05689523942120527</v>
+        <v>0.04954421353677042</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.02945679381882823</v>
+        <v>0.02474417308268423</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.09754602349237416</v>
+        <v>0.08404285300405875</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>15823</v>
+        <v>19066</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>10185</v>
+        <v>12878</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>23533</v>
+        <v>27663</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.05513721885478787</v>
+        <v>0.05760728916913549</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.03549174882443783</v>
+        <v>0.03891023118049174</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.08200254029679969</v>
+        <v>0.08358361342559462</v>
       </c>
     </row>
     <row r="24">
@@ -4535,67 +4535,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>38411</v>
+        <v>45555</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>29142</v>
+        <v>35627</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>47347</v>
+        <v>55866</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2628810292430787</v>
+        <v>0.2692468736906807</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1994447722021578</v>
+        <v>0.2105639671308118</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.3240368709219875</v>
+        <v>0.3301842861111029</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>26423</v>
+        <v>28996</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>20114</v>
+        <v>21368</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>34801</v>
+        <v>38135</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1875815464423093</v>
+        <v>0.1792502301622678</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1427948760001176</v>
+        <v>0.1320968748424932</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.2470539155150621</v>
+        <v>0.2357471716076185</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>64834</v>
+        <v>74551</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>54293</v>
+        <v>61632</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>77964</v>
+        <v>88164</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.225920691347074</v>
+        <v>0.2252592703845292</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.1891890961447922</v>
+        <v>0.1862232685854894</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2716737116926486</v>
+        <v>0.2663898116870153</v>
       </c>
     </row>
     <row r="25">
@@ -4606,67 +4606,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>89303</v>
+        <v>101996</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>78863</v>
+        <v>90611</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>99403</v>
+        <v>112451</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.6111779411831626</v>
+        <v>0.6028275106476552</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.5397216160152197</v>
+        <v>0.5355371430074833</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.6802954087928583</v>
+        <v>0.6646214157023453</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>145</v>
+        <v>170</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>101314</v>
+        <v>119641</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>91686</v>
+        <v>109636</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>109035</v>
+        <v>128729</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.7192430058881791</v>
+        <v>0.7396128535915915</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6508905961501971</v>
+        <v>0.6777611203601502</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.7740532661856092</v>
+        <v>0.7957928863995585</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>267</v>
+        <v>310</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>190617</v>
+        <v>221637</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>177759</v>
+        <v>206336</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>203761</v>
+        <v>236007</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.6642210851423161</v>
+        <v>0.6696839973744537</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.6194158772467631</v>
+        <v>0.6234508966978168</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.7100231759979306</v>
+        <v>0.7131017095837028</v>
       </c>
     </row>
     <row r="26">
@@ -4683,40 +4683,40 @@
         <v>9894</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>5843</v>
+        <v>5867</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>16355</v>
+        <v>16499</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.06771004364653679</v>
+        <v>0.05847412324916442</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.03998642820264519</v>
+        <v>0.0346775362543552</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.1119280317493969</v>
+        <v>0.09751295386277976</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>7</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>5111</v>
+        <v>5110</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>2089</v>
+        <v>2119</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>10225</v>
+        <v>9784</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.0362802082483063</v>
+        <v>0.03159270270937035</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.01482852288284377</v>
+        <v>0.01310148177553243</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.07259198499105289</v>
+        <v>0.06048199173424985</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>20</v>
@@ -4725,19 +4725,19 @@
         <v>15004</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>10093</v>
+        <v>9616</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>23141</v>
+        <v>23246</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.05228288142541013</v>
+        <v>0.04533530810394201</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.03516848899640694</v>
+        <v>0.02905445186981424</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.08063635228010881</v>
+        <v>0.07023754929991835</v>
       </c>
     </row>
     <row r="27">
@@ -4748,16 +4748,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>146117</v>
+        <v>169196</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -4769,16 +4769,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>140862</v>
+        <v>161762</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -4790,16 +4790,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>398</v>
+        <v>459</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>286978</v>
+        <v>330958</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -4829,19 +4829,19 @@
         <v>49893</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>40373</v>
+        <v>39257</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>62860</v>
+        <v>61263</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.09517553857995151</v>
+        <v>0.0790071602179829</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.07701526912698325</v>
+        <v>0.0621653092029538</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1199111714694741</v>
+        <v>0.09701254255830065</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>45</v>
@@ -4850,19 +4850,19 @@
         <v>28947</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>21942</v>
+        <v>21330</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>38638</v>
+        <v>37770</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.05941582670356314</v>
+        <v>0.05012595175945889</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.04503704017761716</v>
+        <v>0.03693643464520396</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.07930639473648537</v>
+        <v>0.06540279238725248</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>117</v>
@@ -4871,19 +4871,19 @@
         <v>78840</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>65138</v>
+        <v>66489</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>94282</v>
+        <v>94830</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.07795015668913016</v>
+        <v>0.06521164604088794</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.06440288371088079</v>
+        <v>0.05499520384656755</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.09321717571063129</v>
+        <v>0.07843698128650946</v>
       </c>
     </row>
     <row r="29">
@@ -4894,67 +4894,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>62674</v>
+        <v>78089</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>51193</v>
+        <v>64799</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>75448</v>
+        <v>93247</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1195570572329769</v>
+        <v>0.1236559899370605</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09765447306179886</v>
+        <v>0.1026112336879394</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1439241473673319</v>
+        <v>0.1476601083961345</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>38866</v>
+        <v>45116</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>29688</v>
+        <v>35743</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>49259</v>
+        <v>55714</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07977506961950961</v>
+        <v>0.07812431973573913</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.06093624757692553</v>
+        <v>0.06189315751584948</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1011070846613938</v>
+        <v>0.09647590010222286</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>101541</v>
+        <v>123205</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>86375</v>
+        <v>106465</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>117697</v>
+        <v>140019</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1003941531417287</v>
+        <v>0.101907149244636</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.08539951592246428</v>
+        <v>0.08806077074210729</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1163683341045885</v>
+        <v>0.115814276570345</v>
       </c>
     </row>
     <row r="30">
@@ -4965,67 +4965,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>125233</v>
+        <v>156079</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>110034</v>
+        <v>140160</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>140312</v>
+        <v>174687</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.23889425466918</v>
+        <v>0.2471556176340138</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.2099005159746317</v>
+        <v>0.2219472729403012</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2676580452636066</v>
+        <v>0.2766229547962112</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>101672</v>
+        <v>122865</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>87514</v>
+        <v>107239</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>116604</v>
+        <v>139031</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2086876950611254</v>
+        <v>0.2127557961254483</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1796266552291893</v>
+        <v>0.1856983703716776</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.239335498468346</v>
+        <v>0.2407488064247911</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>325</v>
+        <v>403</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>226906</v>
+        <v>278944</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>205350</v>
+        <v>257609</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>249456</v>
+        <v>305661</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.2243438151506738</v>
+        <v>0.2307240605545215</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.2030314735056603</v>
+        <v>0.2130775566749106</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2466391477760726</v>
+        <v>0.2528231540567366</v>
       </c>
     </row>
     <row r="31">
@@ -5036,67 +5036,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>364</v>
+        <v>450</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>254976</v>
+        <v>315995</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>235846</v>
+        <v>296682</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>272198</v>
+        <v>336092</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4863894319041682</v>
+        <v>0.5003875219920444</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4498971789407189</v>
+        <v>0.469805520337693</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5192433282162127</v>
+        <v>0.5322118045669378</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>445</v>
+        <v>540</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>298703</v>
+        <v>361554</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>281624</v>
+        <v>342785</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>315262</v>
+        <v>380221</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6131033684668857</v>
+        <v>0.6260765010018331</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5780478453230969</v>
+        <v>0.5935761286545423</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.6470898548161683</v>
+        <v>0.6584007070238873</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>809</v>
+        <v>990</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>553679</v>
+        <v>677549</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>528303</v>
+        <v>650816</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>579459</v>
+        <v>708883</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.5474272824250871</v>
+        <v>0.5604246251598093</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.5223376615531508</v>
+        <v>0.53831271524308</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5729154089105897</v>
+        <v>0.5863415003871727</v>
       </c>
     </row>
     <row r="32">
@@ -5113,19 +5113,19 @@
         <v>31445</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>23399</v>
+        <v>22996</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>41548</v>
+        <v>42177</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.05998371761372345</v>
+        <v>0.0497937102188984</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.04463589268295169</v>
+        <v>0.03641539584030222</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.07925688276476886</v>
+        <v>0.06678878240000873</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>29</v>
@@ -5134,19 +5134,19 @@
         <v>19010</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>13339</v>
+        <v>13002</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>26892</v>
+        <v>26864</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.03901804014891608</v>
+        <v>0.03291743137752063</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02737838002734913</v>
+        <v>0.02251391871343842</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05519763710299874</v>
+        <v>0.04651842499133328</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>72</v>
@@ -5155,19 +5155,19 @@
         <v>50454</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>40692</v>
+        <v>39663</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>62231</v>
+        <v>63180</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.04988459259338034</v>
+        <v>0.04173251900014519</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.0402323219481169</v>
+        <v>0.03280642049981401</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.06152805684246164</v>
+        <v>0.05225813357009278</v>
       </c>
     </row>
     <row r="33">
@@ -5178,16 +5178,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -5199,16 +5199,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -5220,16 +5220,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -5301,7 +5301,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5913,19 +5913,19 @@
         <v>11055</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>7486</v>
+        <v>7189</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>16443</v>
+        <v>16045</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1580614549780998</v>
+        <v>0.1519142540059264</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.1070376742719517</v>
+        <v>0.09878868894601994</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.2350901613690989</v>
+        <v>0.2204847282494443</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>11</v>
@@ -5934,19 +5934,19 @@
         <v>5415</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>3016</v>
+        <v>2762</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>9376</v>
+        <v>9167</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.1058745758809757</v>
+        <v>0.09977570864105242</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.05897500749796709</v>
+        <v>0.05089334004476626</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1833236073443115</v>
+        <v>0.1689216267152704</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>34</v>
@@ -5955,19 +5955,19 @@
         <v>16470</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>11509</v>
+        <v>11618</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>22616</v>
+        <v>22668</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1360194975641806</v>
+        <v>0.1296422192000423</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.09504844846220351</v>
+        <v>0.09144951741667912</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.186775766041571</v>
+        <v>0.1784288042379579</v>
       </c>
     </row>
     <row r="11">
@@ -5978,67 +5978,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>11962</v>
+        <v>12417</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>7492</v>
+        <v>8081</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>19080</v>
+        <v>19310</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1710244137078497</v>
+        <v>0.1706280032039068</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.1071232987312927</v>
+        <v>0.1110438472781341</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.2727992855799825</v>
+        <v>0.2653533439810781</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>7824</v>
+        <v>8393</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>4513</v>
+        <v>4961</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>12515</v>
+        <v>13132</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1529781043954731</v>
+        <v>0.1546558394188458</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.08824108117479934</v>
+        <v>0.09140920332601907</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.2447204847538308</v>
+        <v>0.241977262857745</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>19785</v>
+        <v>20810</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>13557</v>
+        <v>14690</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>26749</v>
+        <v>27976</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1634022682907703</v>
+        <v>0.1638051702066168</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.1119608508310845</v>
+        <v>0.1156290855017593</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.2209091387591327</v>
+        <v>0.2202145421384262</v>
       </c>
     </row>
     <row r="12">
@@ -6049,67 +6049,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>11784</v>
+        <v>12242</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>7604</v>
+        <v>7986</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>17399</v>
+        <v>18156</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.1684807430398061</v>
+        <v>0.1682268967238302</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1087256959046794</v>
+        <v>0.1097365977303388</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.2487650459043143</v>
+        <v>0.2494879735866226</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>7416</v>
+        <v>8841</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>4468</v>
+        <v>5388</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>12689</v>
+        <v>13577</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1450072558359867</v>
+        <v>0.1629168588503287</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.08736243964592066</v>
+        <v>0.09928404397801889</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2481078599894836</v>
+        <v>0.2501851760786415</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>19200</v>
+        <v>21083</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>13457</v>
+        <v>15348</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>26214</v>
+        <v>28329</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.1585663428255331</v>
+        <v>0.1659586065843268</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1111383317127655</v>
+        <v>0.1208139143214695</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2164939672635456</v>
+        <v>0.2229920614802102</v>
       </c>
     </row>
     <row r="13">
@@ -6120,67 +6120,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>32629</v>
+        <v>34545</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>25859</v>
+        <v>27734</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>39021</v>
+        <v>41064</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4665110687179691</v>
+        <v>0.4747055889230932</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.369717573982805</v>
+        <v>0.3811028857800765</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5579060620531023</v>
+        <v>0.5642836945188804</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>28591</v>
+        <v>29722</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>22936</v>
+        <v>24403</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>33708</v>
+        <v>34815</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5590442231878904</v>
+        <v>0.5476926450831571</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4484834642560128</v>
+        <v>0.4496790564087039</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.6591061775687476</v>
+        <v>0.6415439335331011</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>61219</v>
+        <v>64267</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>52953</v>
+        <v>55306</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>69907</v>
+        <v>73168</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5055939164660731</v>
+        <v>0.5058834870366663</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.437324091815029</v>
+        <v>0.4353429876954326</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.577342272101201</v>
+        <v>0.5759476683710121</v>
       </c>
     </row>
     <row r="14">
@@ -6197,19 +6197,19 @@
         <v>2512</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>988</v>
+        <v>842</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>5850</v>
+        <v>5680</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.03592231955627551</v>
+        <v>0.03452525714324347</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.0141207800866936</v>
+        <v>0.0115772171982297</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.08363554805491474</v>
+        <v>0.07804747639922077</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>3</v>
@@ -6218,19 +6218,19 @@
         <v>1897</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>5155</v>
+        <v>5249</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.03709584069967403</v>
+        <v>0.0349589480066162</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.008415689051298249</v>
+        <v>0.007829039768197616</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1007975451160168</v>
+        <v>0.09671868022972893</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>8</v>
@@ -6239,19 +6239,19 @@
         <v>4410</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>1992</v>
+        <v>1925</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>9066</v>
+        <v>8729</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.03641797485344291</v>
+        <v>0.03471051697234753</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.01645387528222432</v>
+        <v>0.01515158566645443</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.07487146179900211</v>
+        <v>0.06870717407012476</v>
       </c>
     </row>
     <row r="15">
@@ -6262,16 +6262,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>69942</v>
+        <v>72772</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -6283,16 +6283,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>51142</v>
+        <v>54268</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -6304,16 +6304,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>121084</v>
+        <v>127040</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -6343,19 +6343,19 @@
         <v>6581</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>2870</v>
+        <v>2942</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>12134</v>
+        <v>12630</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.07071753092127245</v>
+        <v>0.06626341491706758</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.03084207171304728</v>
+        <v>0.02962348159699365</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1303924876171604</v>
+        <v>0.1271705377981565</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>2</v>
@@ -6367,16 +6367,16 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>3035</v>
+        <v>3307</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01240026575707054</v>
+        <v>0.01129941674986616</v>
       </c>
       <c r="O16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.04393850235849637</v>
+        <v>0.0436222743299172</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>10</v>
@@ -6385,19 +6385,19 @@
         <v>7437</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>3371</v>
+        <v>3366</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>13109</v>
+        <v>13019</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.04587049206718118</v>
+        <v>0.0424691974108912</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.02078879314061974</v>
+        <v>0.0192181379648026</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.08084763819718635</v>
+        <v>0.07434179254718214</v>
       </c>
     </row>
     <row r="17">
@@ -6414,61 +6414,61 @@
         <v>16523</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>10702</v>
+        <v>10606</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>24134</v>
+        <v>23788</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1775560716354605</v>
+        <v>0.166372771964044</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.115009398913388</v>
+        <v>0.1067994751361988</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.2593432458713952</v>
+        <v>0.2395306827743829</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>7491</v>
+        <v>8820</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>4055</v>
+        <v>4948</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>12846</v>
+        <v>14749</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1084372188780493</v>
+        <v>0.1163399313328606</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.05870350151814923</v>
+        <v>0.0652699048972829</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1859521609368558</v>
+        <v>0.1945460914440113</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>24014</v>
+        <v>25343</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>17082</v>
+        <v>18310</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>33474</v>
+        <v>34636</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1481068370875442</v>
+        <v>0.1447132797122478</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.1053540991795841</v>
+        <v>0.1045554031440588</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.2064542542579777</v>
+        <v>0.1977785607435507</v>
       </c>
     </row>
     <row r="18">
@@ -6479,67 +6479,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>18884</v>
+        <v>21514</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>12801</v>
+        <v>14721</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>27878</v>
+        <v>30034</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.202927171784365</v>
+        <v>0.2166304252887536</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1375601597909151</v>
+        <v>0.1482258975094935</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.2995812987116497</v>
+        <v>0.3024156688385043</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>18038</v>
+        <v>20115</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>12070</v>
+        <v>14217</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>24133</v>
+        <v>26716</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.2611109908149093</v>
+        <v>0.2653279394442024</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1747215125487789</v>
+        <v>0.1875249313301683</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.3493317941506939</v>
+        <v>0.3524026636042855</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>36922</v>
+        <v>41629</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>27777</v>
+        <v>32555</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>48008</v>
+        <v>53073</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.2277173536980873</v>
+        <v>0.237711847355249</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1713133934638367</v>
+        <v>0.1858956150458013</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.296093620204044</v>
+        <v>0.3030594268405329</v>
       </c>
     </row>
     <row r="19">
@@ -6550,67 +6550,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>48508</v>
+        <v>52133</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>39400</v>
+        <v>42939</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>57765</v>
+        <v>61098</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.5212735527743156</v>
+        <v>0.5249414086778457</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.4233986373631821</v>
+        <v>0.4323691386425008</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.6207481633345872</v>
+        <v>0.6152147102430843</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>39897</v>
+        <v>43221</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>33213</v>
+        <v>35855</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>46363</v>
+        <v>50172</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5775321223766283</v>
+        <v>0.5701104705968458</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.480776540436764</v>
+        <v>0.4729453875068013</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.671122729636099</v>
+        <v>0.6617919833253113</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>88405</v>
+        <v>95354</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>77789</v>
+        <v>83156</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>99711</v>
+        <v>107600</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5452434502111785</v>
+        <v>0.5444953443391705</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4797703678428166</v>
+        <v>0.4748390050981794</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.614970396237795</v>
+        <v>0.6144203264242651</v>
       </c>
     </row>
     <row r="20">
@@ -6627,19 +6627,19 @@
         <v>2561</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>7019</v>
+        <v>7135</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.02752567288458662</v>
+        <v>0.02579197915228939</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.007026334679268175</v>
+        <v>0.006659971115999229</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.07542649300091249</v>
+        <v>0.07183931463801248</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>4</v>
@@ -6648,19 +6648,19 @@
         <v>2799</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>6798</v>
+        <v>6635</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.04051940217334243</v>
+        <v>0.036922241876225</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.009630523003178159</v>
+        <v>0.008661602343175619</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.09840922870581083</v>
+        <v>0.08752163088297905</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>7</v>
@@ -6669,19 +6669,19 @@
         <v>5361</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>2239</v>
+        <v>2287</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>10893</v>
+        <v>10351</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.03306186693600871</v>
+        <v>0.03061033118244148</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.01380736462575727</v>
+        <v>0.01306142421507196</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.06718176869567058</v>
+        <v>0.05910817250679266</v>
       </c>
     </row>
     <row r="21">
@@ -6692,16 +6692,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>93057</v>
+        <v>99312</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -6713,16 +6713,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>69082</v>
+        <v>75812</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -6734,16 +6734,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>162139</v>
+        <v>175124</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -6776,16 +6776,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>6085</v>
+        <v>6479</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01470285218125158</v>
+        <v>0.0140780343475879</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.04889547558841707</v>
+        <v>0.04985464880743152</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>3</v>
@@ -6794,19 +6794,19 @@
         <v>2652</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>657</v>
+        <v>642</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>8530</v>
+        <v>7677</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.02564749296419586</v>
+        <v>0.02502616232825959</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.00635417995017828</v>
+        <v>0.006056859722929958</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.08250253879869909</v>
+        <v>0.07245793778254393</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>5</v>
@@ -6815,19 +6815,19 @@
         <v>4481</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>1616</v>
+        <v>1460</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>10985</v>
+        <v>10358</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.01966945880892297</v>
+        <v>0.01899497696330502</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.007092124409547016</v>
+        <v>0.006187148356427286</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.04821634303193092</v>
+        <v>0.04390423707314459</v>
       </c>
     </row>
     <row r="23">
@@ -6844,19 +6844,19 @@
         <v>9919</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>5063</v>
+        <v>4681</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>16876</v>
+        <v>17318</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.07971052399849948</v>
+        <v>0.07632311614654219</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.04068437017543228</v>
+        <v>0.0360146962166259</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1356122592162628</v>
+        <v>0.1332544941456556</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>3</v>
@@ -6865,19 +6865,19 @@
         <v>1742</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>5092</v>
+        <v>4593</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.01685239997079303</v>
+        <v>0.01644413736183073</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.004604165606284423</v>
+        <v>0.004509716966023571</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.04925058929489563</v>
+        <v>0.0433452684571665</v>
       </c>
       <c r="Q23" s="5" t="n">
         <v>14</v>
@@ -6886,19 +6886,19 @@
         <v>11661</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>6065</v>
+        <v>6701</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>19322</v>
+        <v>20331</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.05118591715297328</v>
+        <v>0.04943071014873565</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.02661933453708393</v>
+        <v>0.02840537912501899</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.08480922381581738</v>
+        <v>0.08617858273806231</v>
       </c>
     </row>
     <row r="24">
@@ -6909,25 +6909,25 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>28496</v>
+        <v>30898</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>20320</v>
+        <v>20933</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>41188</v>
+        <v>42815</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2289940731783136</v>
+        <v>0.2377426325110815</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1632935077596887</v>
+        <v>0.1610666342603173</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.3309892273653076</v>
+        <v>0.3294429968414229</v>
       </c>
       <c r="J24" s="5" t="n">
         <v>15</v>
@@ -6936,40 +6936,40 @@
         <v>10875</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>6097</v>
+        <v>6185</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>16916</v>
+        <v>17310</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1051844812990726</v>
+        <v>0.1026363047288552</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.05896918606485852</v>
+        <v>0.05837910650817867</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.1636214658735972</v>
+        <v>0.1633701535482687</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>39371</v>
+        <v>41772</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>29297</v>
+        <v>31220</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>53119</v>
+        <v>56266</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.1728100876285103</v>
+        <v>0.1770646735122211</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.1285949910371779</v>
+        <v>0.132337176162433</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2331563409485833</v>
+        <v>0.2385016717359377</v>
       </c>
     </row>
     <row r="25">
@@ -6980,67 +6980,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>76365</v>
+        <v>79486</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>65378</v>
+        <v>68473</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>87672</v>
+        <v>90235</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.6136668358831551</v>
+        <v>0.6116046166386173</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.5253764758143584</v>
+        <v>0.5268682974630974</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.7045343370127625</v>
+        <v>0.6943152590954719</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>84545</v>
+        <v>87112</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>76818</v>
+        <v>79394</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>90784</v>
+        <v>93241</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.8177612221758819</v>
+        <v>0.8221760995237681</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.7430180779476442</v>
+        <v>0.7493313668433015</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.87810931225488</v>
+        <v>0.8800196065088274</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>160910</v>
+        <v>166598</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>147291</v>
+        <v>152155</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>173632</v>
+        <v>179148</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.7062835376767514</v>
+        <v>0.7061749303653686</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.6465072472396126</v>
+        <v>0.644955916841876</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.7621268162772368</v>
+        <v>0.7593702799728739</v>
       </c>
     </row>
     <row r="26">
@@ -7057,19 +7057,19 @@
         <v>7830</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>3777</v>
+        <v>4166</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>13521</v>
+        <v>13314</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.0629257147587803</v>
+        <v>0.06025160035617105</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.03034915399637395</v>
+        <v>0.03205790517979081</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.1086546067611368</v>
+        <v>0.1024446084172367</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>6</v>
@@ -7078,19 +7078,19 @@
         <v>3572</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1515</v>
+        <v>1372</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>8519</v>
+        <v>7747</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.03455440359005681</v>
+        <v>0.03371729605728625</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.01465069071333005</v>
+        <v>0.0129532395553049</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.0823991550515102</v>
+        <v>0.07311770302056815</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>17</v>
@@ -7099,19 +7099,19 @@
         <v>11403</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>6747</v>
+        <v>6779</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>17680</v>
+        <v>17886</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.05005099873284208</v>
+        <v>0.04833470901036966</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.02961431032303204</v>
+        <v>0.02873607444422021</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.0776039692567323</v>
+        <v>0.07581510381129167</v>
       </c>
     </row>
     <row r="27">
@@ -7122,16 +7122,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>124440</v>
+        <v>129963</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -7143,16 +7143,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>103386</v>
+        <v>105953</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -7164,16 +7164,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>227826</v>
+        <v>235916</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -7203,19 +7203,19 @@
         <v>20534</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>14690</v>
+        <v>14668</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>28221</v>
+        <v>28648</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.06953390192572956</v>
+        <v>0.06625640786564475</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.04974470096925213</v>
+        <v>0.04732664215100515</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.09556382909035477</v>
+        <v>0.09243540000168564</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>18</v>
@@ -7224,19 +7224,19 @@
         <v>9822</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>5984</v>
+        <v>5952</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>16025</v>
+        <v>15677</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.04158010159618866</v>
+        <v>0.03950258751054814</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.0253303468865386</v>
+        <v>0.02393648321984446</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.06784006227418887</v>
+        <v>0.06305217076505047</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>54</v>
@@ -7245,19 +7245,19 @@
         <v>30356</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>23056</v>
+        <v>21832</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>39654</v>
+        <v>39931</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.0571109569111312</v>
+        <v>0.05434710160472543</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.04337620179188037</v>
+        <v>0.03908605202554562</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.07460204759140737</v>
+        <v>0.07148771338274433</v>
       </c>
     </row>
     <row r="29">
@@ -7268,67 +7268,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>38404</v>
+        <v>38859</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>28527</v>
+        <v>29036</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>50639</v>
+        <v>50262</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1300435512930515</v>
+        <v>0.1253826275996551</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09659704987445564</v>
+        <v>0.09368918503665173</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1714747123912722</v>
+        <v>0.1621744021396123</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>17816</v>
+        <v>19715</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>11974</v>
+        <v>13362</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>24843</v>
+        <v>27080</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07542309374672825</v>
+        <v>0.07928893841292615</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.05069207494921473</v>
+        <v>0.05374176233887454</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1051679823534004</v>
+        <v>0.1089122094984304</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>56220</v>
+        <v>58574</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>45394</v>
+        <v>46661</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>70464</v>
+        <v>72699</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1057696803785088</v>
+        <v>0.104864292127024</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.08540154257041084</v>
+        <v>0.08353730110616554</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1325670641041694</v>
+        <v>0.1301536378381803</v>
       </c>
     </row>
     <row r="30">
@@ -7339,67 +7339,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>62400</v>
+        <v>67890</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>48531</v>
+        <v>55392</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>75793</v>
+        <v>83600</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2113003858910899</v>
+        <v>0.2190557688248159</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.164335334888596</v>
+        <v>0.178727015457265</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.256651485697376</v>
+        <v>0.2697440014259118</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>38442</v>
+        <v>41944</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>29966</v>
+        <v>33725</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>48884</v>
+        <v>53835</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1627388332431797</v>
+        <v>0.1686933285679346</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1268576154895797</v>
+        <v>0.1356363775929846</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2069432250850004</v>
+        <v>0.2165149259071954</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>100842</v>
+        <v>109835</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>83743</v>
+        <v>93271</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>117490</v>
+        <v>128619</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.1897191521677102</v>
+        <v>0.1966372238429889</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.1575502098463926</v>
+        <v>0.1669828629768384</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2210401311171179</v>
+        <v>0.2302665262046047</v>
       </c>
     </row>
     <row r="31">
@@ -7410,67 +7410,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>160681</v>
+        <v>169343</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>144308</v>
+        <v>152814</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>176241</v>
+        <v>184409</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.5440988934224992</v>
+        <v>0.5464041087557022</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4886578117298992</v>
+        <v>0.4930720308199934</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5967897434437842</v>
+        <v>0.5950156463513958</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>158394</v>
+        <v>165416</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>146846</v>
+        <v>152442</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>170720</v>
+        <v>176874</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6705382862218142</v>
+        <v>0.6652796617098348</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6216523767872832</v>
+        <v>0.613098227416492</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.7227203048937656</v>
+        <v>0.7113613830495057</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>319074</v>
+        <v>334760</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>299339</v>
+        <v>315001</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>339037</v>
+        <v>355396</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.60028980864361</v>
+        <v>0.5993208641303116</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.563160768622505</v>
+        <v>0.5639471153154629</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.6378464072351873</v>
+        <v>0.6362654989695848</v>
       </c>
     </row>
     <row r="32">
@@ -7487,19 +7487,19 @@
         <v>13296</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>7812</v>
+        <v>8334</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>20024</v>
+        <v>20131</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.04502326746762988</v>
+        <v>0.04290108695418218</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.0264528256244437</v>
+        <v>0.02689121781838753</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.06780558474788687</v>
+        <v>0.06495411129809432</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>18</v>
@@ -7508,19 +7508,19 @@
         <v>11745</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>6923</v>
+        <v>7109</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>18359</v>
+        <v>18101</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.04971968519208925</v>
+        <v>0.04723548379875631</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02930601463734402</v>
+        <v>0.02859167592456736</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07772119987038033</v>
+        <v>0.07279780441381759</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>38</v>
@@ -7529,19 +7529,19 @@
         <v>25041</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>17719</v>
+        <v>17996</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>33945</v>
+        <v>33671</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.04711040189903985</v>
+        <v>0.04483051829495001</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.03333524867077534</v>
+        <v>0.03221805119402989</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.06386237884781724</v>
+        <v>0.06028176938657121</v>
       </c>
     </row>
     <row r="33">
@@ -7552,16 +7552,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -7573,16 +7573,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -7594,16 +7594,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
